--- a/Sergio i Dome/PF_SergioCastañeirasMorales_DomènecHuertaestradé_T18.xlsx
+++ b/Sergio i Dome/PF_SergioCastañeirasMorales_DomènecHuertaestradé_T18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deumenec/Documents/Uni/LACE/Sergio i Dome/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D933AAF7-A9B8-5F40-AD1C-97744B04E492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC1888B-ED1A-464D-B73B-8065356E7D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
   </bookViews>
